--- a/tooldke/code/extracted_data_final_v9.xlsx
+++ b/tooldke/code/extracted_data_final_v9.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,20 +464,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_10_05_11_case01_T0_P0.png</t>
+          <t>2026_07_14_18_26_49_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60.718</v>
+        <v>62.049</v>
       </c>
       <c r="D2" t="n">
-        <v>14.59</v>
+        <v>14.64</v>
       </c>
       <c r="E2" t="n">
-        <v>1.16</v>
+        <v>1.204</v>
       </c>
       <c r="F2" t="n">
-        <v>1.312</v>
+        <v>1.367</v>
       </c>
     </row>
     <row r="3">
@@ -486,20 +486,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_23_59_11_case01_T0_P0.png</t>
+          <t>2026_07_14_18_41_12_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60.721</v>
+        <v>62.299</v>
       </c>
       <c r="D3" t="n">
-        <v>14.49</v>
+        <v>14.38</v>
       </c>
       <c r="E3" t="n">
-        <v>1.138</v>
+        <v>1.145</v>
       </c>
       <c r="F3" t="n">
-        <v>1.312</v>
+        <v>1.315</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +508,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_40_28_11_case01_T0_P0.png</t>
+          <t>2026_07_14_19_43_51_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>61.406</v>
+        <v>62.152</v>
       </c>
       <c r="D4" t="n">
-        <v>16.23</v>
+        <v>13.7</v>
       </c>
       <c r="E4" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1.312</v>
+        <v>1.304</v>
       </c>
     </row>
     <row r="5">
@@ -530,20 +530,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_09_54_34_11_case01_T0_P0.png</t>
+          <t>2026_07_15_07_39_59_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>61.185</v>
+        <v>61.635</v>
       </c>
       <c r="D5" t="n">
-        <v>16.38</v>
+        <v>15.71</v>
       </c>
       <c r="E5" t="n">
-        <v>1.167</v>
+        <v>1.112</v>
       </c>
       <c r="F5" t="n">
-        <v>1.312</v>
+        <v>1.282</v>
       </c>
     </row>
     <row r="6">
@@ -552,42 +552,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_08_54_11_case01_T0_P0.png</t>
+          <t>2026_07_15_07_57_03_11_case01_T0_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61.323</v>
+        <v>61.744</v>
       </c>
       <c r="D6" t="n">
-        <v>15.82</v>
+        <v>14.32</v>
       </c>
       <c r="E6" t="n">
-        <v>1.148</v>
+        <v>1.134</v>
       </c>
       <c r="F6" t="n">
-        <v>1.312</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_23_04_11_case01_T0_P0.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>61.114</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15.09</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.233</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.312</v>
+        <v>1.306</v>
       </c>
     </row>
   </sheetData>
@@ -601,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,20 +620,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_20_59_11_case12_T32_P0.png</t>
+          <t>2026_07_14_18_38_00_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.506</v>
+        <v>17.838</v>
       </c>
       <c r="D2" t="n">
-        <v>14.64</v>
+        <v>14.65</v>
       </c>
       <c r="E2" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="F2" t="n">
-        <v>3.041</v>
+        <v>2.689</v>
       </c>
     </row>
     <row r="3">
@@ -664,20 +642,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_34_53_11_case12_T32_P0.png</t>
+          <t>2026_07_14_18_52_24_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.507</v>
+        <v>17.924</v>
       </c>
       <c r="D3" t="n">
-        <v>14.53</v>
+        <v>14.36</v>
       </c>
       <c r="E3" t="n">
-        <v>2.425</v>
+        <v>2.074</v>
       </c>
       <c r="F3" t="n">
-        <v>2.998</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="4">
@@ -686,20 +664,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_51_21_11_case12_T32_P0.png</t>
+          <t>2026_07_14_19_55_03_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.696</v>
+        <v>17.869</v>
       </c>
       <c r="D4" t="n">
-        <v>16.32</v>
+        <v>13.74</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5</v>
+        <v>2.043</v>
       </c>
       <c r="F4" t="n">
-        <v>3.071</v>
+        <v>2.576</v>
       </c>
     </row>
     <row r="5">
@@ -708,20 +686,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_10_05_24_11_case12_T32_P0.png</t>
+          <t>2026_07_15_07_51_09_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.637</v>
+        <v>17.729</v>
       </c>
       <c r="D5" t="n">
-        <v>16.37</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
-        <v>2.458</v>
+        <v>2.201</v>
       </c>
       <c r="F5" t="n">
-        <v>3.008</v>
+        <v>2.695</v>
       </c>
     </row>
     <row r="6">
@@ -730,42 +708,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_19_45_11_case12_T32_P0.png</t>
+          <t>2026_07_15_08_08_14_11_case12_T32_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.672</v>
+        <v>17.762</v>
       </c>
       <c r="D6" t="n">
-        <v>15.94</v>
+        <v>14.38</v>
       </c>
       <c r="E6" t="n">
-        <v>2.407</v>
+        <v>2.093</v>
       </c>
       <c r="F6" t="n">
-        <v>2.935</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_33_54_11_case12_T32_P0.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>16.614</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.558</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3.103</v>
+        <v>2.637</v>
       </c>
     </row>
   </sheetData>
@@ -779,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -820,20 +776,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_21_44_11_case13_T40_P0.png</t>
+          <t>2026_07_14_18_38_45_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.585</v>
+        <v>16.675</v>
       </c>
       <c r="D2" t="n">
-        <v>14.52</v>
+        <v>14.69</v>
       </c>
       <c r="E2" t="n">
-        <v>2.479</v>
+        <v>2.52</v>
       </c>
       <c r="F2" t="n">
-        <v>3.041</v>
+        <v>3.084</v>
       </c>
     </row>
     <row r="3">
@@ -842,20 +798,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_35_38_11_case13_T40_P0.png</t>
+          <t>2026_07_14_18_53_08_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.586</v>
+        <v>16.75</v>
       </c>
       <c r="D3" t="n">
-        <v>14.52</v>
+        <v>14.3</v>
       </c>
       <c r="E3" t="n">
-        <v>2.432</v>
+        <v>2.437</v>
       </c>
       <c r="F3" t="n">
-        <v>3.005</v>
+        <v>3.026</v>
       </c>
     </row>
     <row r="4">
@@ -864,20 +820,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_52_05_11_case13_T40_P0.png</t>
+          <t>2026_07_14_19_55_48_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.772</v>
+        <v>16.703</v>
       </c>
       <c r="D4" t="n">
-        <v>16.29</v>
+        <v>13.75</v>
       </c>
       <c r="E4" t="n">
-        <v>2.504</v>
+        <v>2.376</v>
       </c>
       <c r="F4" t="n">
-        <v>3.07</v>
+        <v>2.949</v>
       </c>
     </row>
     <row r="5">
@@ -886,20 +842,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_10_06_09_11_case13_T40_P0.png</t>
+          <t>2026_07_15_07_51_53_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.715</v>
+        <v>16.565</v>
       </c>
       <c r="D5" t="n">
-        <v>16.32</v>
+        <v>15.01</v>
       </c>
       <c r="E5" t="n">
-        <v>2.48</v>
+        <v>2.531</v>
       </c>
       <c r="F5" t="n">
-        <v>3.025</v>
+        <v>3.067</v>
       </c>
     </row>
     <row r="6">
@@ -908,42 +864,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_20_29_11_case13_T40_P0.png</t>
+          <t>2026_07_15_08_08_58_11_case13_T40_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.752</v>
+        <v>16.597</v>
       </c>
       <c r="D6" t="n">
-        <v>15.86</v>
+        <v>14.39</v>
       </c>
       <c r="E6" t="n">
-        <v>2.419</v>
+        <v>2.476</v>
       </c>
       <c r="F6" t="n">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_34_39_11_case13_T40_P0.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>16.695</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.584</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3.123</v>
+        <v>3.053</v>
       </c>
     </row>
   </sheetData>
@@ -957,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,19 +932,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_11_45_11_case02_T2_P0.png</t>
+          <t>2026_07_14_18_28_35_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60.713</v>
+        <v>62.036</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>1.203</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.364</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1018,19 +954,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_25_38_11_case02_T2_P0.png</t>
+          <t>2026_07_14_18_42_59_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60.71</v>
+        <v>62.319</v>
       </c>
       <c r="D3" t="n">
-        <v>14.5</v>
+        <v>14.43</v>
       </c>
       <c r="E3" t="n">
-        <v>1.139</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>1.16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.328</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1038,19 +976,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_42_08_11_case02_T2_P0.png</t>
+          <t>2026_07_14_19_45_38_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>61.419</v>
+        <v>62.157</v>
       </c>
       <c r="D4" t="n">
-        <v>16.29</v>
+        <v>13.78</v>
       </c>
       <c r="E4" t="n">
-        <v>1.155</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1.137</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.302</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1058,19 +998,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_09_56_13_11_case02_T2_P0.png</t>
+          <t>2026_07_15_07_41_45_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>61.165</v>
+        <v>61.648</v>
       </c>
       <c r="D5" t="n">
-        <v>16.36</v>
+        <v>14.82</v>
       </c>
       <c r="E5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>1.018</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1078,39 +1020,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_10_33_11_case02_T2_P0.png</t>
+          <t>2026_07_15_07_58_49_11_case02_T2_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61.322</v>
+        <v>61.755</v>
       </c>
       <c r="D6" t="n">
-        <v>15.89</v>
+        <v>14.37</v>
       </c>
       <c r="E6" t="n">
-        <v>1.144</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_24_43_11_case02_T2_P0.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>61.115</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15.03</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.223</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>1.141</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.311</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1123,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,19 +1088,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_13_24_11_case03_T4_P1.png</t>
+          <t>2026_07_14_18_30_15_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>61.009</v>
+        <v>57.354</v>
       </c>
       <c r="D2" t="n">
-        <v>14.56</v>
+        <v>14.62</v>
       </c>
       <c r="E2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>1.258</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1184,19 +1110,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_27_18_11_case03_T4_P1.png</t>
+          <t>2026_07_14_18_44_38_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>61.016</v>
+        <v>57.617</v>
       </c>
       <c r="D3" t="n">
-        <v>14.57</v>
+        <v>14.38</v>
       </c>
       <c r="E3" t="n">
-        <v>1.104</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>1.217</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.418</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1204,19 +1132,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_43_46_11_case03_T4_P1.png</t>
+          <t>2026_07_14_19_47_17_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>61.725</v>
+        <v>57.45</v>
       </c>
       <c r="D4" t="n">
-        <v>16.31</v>
+        <v>13.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1.136</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1.189</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.382</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1224,19 +1154,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_09_57_52_11_case03_T4_P1.png</t>
+          <t>2026_07_15_07_43_25_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>61.47</v>
+        <v>56.976</v>
       </c>
       <c r="D5" t="n">
-        <v>16.31</v>
+        <v>14.9</v>
       </c>
       <c r="E5" t="n">
-        <v>1.149</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>1.258</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.442</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,39 +1176,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_12_12_11_case03_T4_P1.png</t>
+          <t>2026_07_15_08_00_29_11_case03_T4_P1.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>61.63</v>
+        <v>57.092</v>
       </c>
       <c r="D6" t="n">
-        <v>15.87</v>
+        <v>14.33</v>
       </c>
       <c r="E6" t="n">
-        <v>1.115</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_26_22_11_case03_T4_P1.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>61.416</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.201</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>1.194</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.397</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1289,7 +1203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1330,17 +1244,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_15_04_11_case04_T6_P0.png</t>
+          <t>2026_07_14_18_31_54_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.743</v>
+        <v>40.674</v>
       </c>
       <c r="D2" t="n">
         <v>14.59</v>
       </c>
       <c r="E2" t="n">
-        <v>1.169</v>
+        <v>1.18</v>
       </c>
       <c r="F2" t="n">
         <v>1.347</v>
@@ -1352,20 +1266,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_28_56_11_case04_T6_P0.png</t>
+          <t>2026_07_14_18_46_18_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.736</v>
+        <v>40.856</v>
       </c>
       <c r="D3" t="n">
-        <v>14.5</v>
+        <v>14.39</v>
       </c>
       <c r="E3" t="n">
-        <v>1.123</v>
+        <v>1.11</v>
       </c>
       <c r="F3" t="n">
-        <v>1.303</v>
+        <v>1.285</v>
       </c>
     </row>
     <row r="4">
@@ -1374,20 +1288,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_45_26_11_case04_T6_P0.png</t>
+          <t>2026_07_14_19_48_57_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.202</v>
+        <v>40.743</v>
       </c>
       <c r="D4" t="n">
-        <v>16.3</v>
+        <v>13.74</v>
       </c>
       <c r="E4" t="n">
-        <v>1.157</v>
+        <v>1.101</v>
       </c>
       <c r="F4" t="n">
-        <v>1.339</v>
+        <v>1.272</v>
       </c>
     </row>
     <row r="5">
@@ -1396,20 +1310,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_09_59_31_11_case04_T6_P0.png</t>
+          <t>2026_07_15_07_45_03_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41.056</v>
+        <v>40.397</v>
       </c>
       <c r="D5" t="n">
-        <v>16.33</v>
+        <v>14.94</v>
       </c>
       <c r="E5" t="n">
-        <v>1.165</v>
+        <v>1.179</v>
       </c>
       <c r="F5" t="n">
-        <v>1.336</v>
+        <v>1.341</v>
       </c>
     </row>
     <row r="6">
@@ -1418,42 +1332,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_13_51_11_case04_T6_P0.png</t>
+          <t>2026_07_15_08_02_08_11_case04_T6_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41.153</v>
+        <v>40.467</v>
       </c>
       <c r="D6" t="n">
-        <v>15.94</v>
+        <v>14.35</v>
       </c>
       <c r="E6" t="n">
-        <v>1.13</v>
+        <v>1.092</v>
       </c>
       <c r="F6" t="n">
-        <v>1.295</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_28_01_11_case04_T6_P0.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.397</v>
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>
@@ -1467,7 +1359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1508,20 +1400,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_16_30_11_case05_T8_P0.png</t>
+          <t>2026_07_14_18_33_21_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.705</v>
+        <v>40.631</v>
       </c>
       <c r="D2" t="n">
-        <v>14.58</v>
+        <v>14.62</v>
       </c>
       <c r="E2" t="n">
-        <v>1.175</v>
+        <v>1.188</v>
       </c>
       <c r="F2" t="n">
-        <v>1.351</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="3">
@@ -1530,20 +1422,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_30_25_11_case05_T8_P0.png</t>
+          <t>2026_07_14_18_47_44_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.691</v>
+        <v>40.808</v>
       </c>
       <c r="D3" t="n">
-        <v>14.51</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1.134</v>
+        <v>1.118</v>
       </c>
       <c r="F3" t="n">
-        <v>1.314</v>
+        <v>1.294</v>
       </c>
     </row>
     <row r="4">
@@ -1552,20 +1444,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_46_52_11_case05_T8_P0.png</t>
+          <t>2026_07_14_19_50_23_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.167</v>
+        <v>40.695</v>
       </c>
       <c r="D4" t="n">
-        <v>16.31</v>
+        <v>13.73</v>
       </c>
       <c r="E4" t="n">
-        <v>1.169</v>
+        <v>1.067</v>
       </c>
       <c r="F4" t="n">
-        <v>1.349</v>
+        <v>1.242</v>
       </c>
     </row>
     <row r="5">
@@ -1574,20 +1466,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_10_00_57_11_case05_T8_P0.png</t>
+          <t>2026_07_15_07_46_29_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>41.011</v>
+        <v>40.371</v>
       </c>
       <c r="D5" t="n">
-        <v>16.41</v>
+        <v>15.01</v>
       </c>
       <c r="E5" t="n">
-        <v>1.184</v>
+        <v>1.17</v>
       </c>
       <c r="F5" t="n">
-        <v>1.354</v>
+        <v>1.331</v>
       </c>
     </row>
     <row r="6">
@@ -1596,42 +1488,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_15_18_11_case05_T8_P0.png</t>
+          <t>2026_07_15_08_03_34_11_case05_T8_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>41.105</v>
+        <v>40.424</v>
       </c>
       <c r="D6" t="n">
-        <v>15.99</v>
+        <v>14.32</v>
       </c>
       <c r="E6" t="n">
-        <v>1.159</v>
+        <v>1.12</v>
       </c>
       <c r="F6" t="n">
-        <v>1.322</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_29_27_11_case05_T8_P0.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>40.959</v>
-      </c>
-      <c r="D7" t="n">
-        <v>14.99</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.223</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.39</v>
+        <v>1.292</v>
       </c>
     </row>
   </sheetData>
@@ -1645,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1686,19 +1556,21 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_17_42_11_case06_T10_P0.png</t>
+          <t>2026_07_14_18_34_40_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.558</v>
+        <v>40.654</v>
       </c>
       <c r="D2" t="n">
-        <v>14.52</v>
+        <v>14.66</v>
       </c>
       <c r="E2" t="n">
-        <v>1.143</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>1.233</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.402</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1706,19 +1578,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_31_36_11_case06_T10_P0.png</t>
+          <t>2026_07_14_18_49_03_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40.56</v>
+        <v>40.842</v>
       </c>
       <c r="D3" t="n">
-        <v>14.54</v>
+        <v>14.37</v>
       </c>
       <c r="E3" t="n">
-        <v>1.129</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>1.151</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.333</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1726,19 +1600,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_48_04_11_case06_T10_P0.png</t>
+          <t>2026_07_14_19_51_42_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41.029</v>
+        <v>40.742</v>
       </c>
       <c r="D4" t="n">
-        <v>16.24</v>
+        <v>13.78</v>
       </c>
       <c r="E4" t="n">
-        <v>1.193</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>1.098</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.281</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1746,19 +1622,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_10_02_08_11_case06_T10_P0.png</t>
+          <t>2026_07_15_07_47_48_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40.867</v>
+        <v>40.398</v>
       </c>
       <c r="D5" t="n">
-        <v>16.41</v>
+        <v>14.93</v>
       </c>
       <c r="E5" t="n">
-        <v>1.184</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>1.212</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.377</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1766,39 +1644,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_16_28_11_case06_T10_P0.png</t>
+          <t>2026_07_15_08_04_53_11_case06_T10_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40.971</v>
+        <v>40.463</v>
       </c>
       <c r="D6" t="n">
-        <v>15.94</v>
+        <v>14.35</v>
       </c>
       <c r="E6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_30_38_11_case06_T10_P0.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>40.825</v>
-      </c>
-      <c r="D7" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.213</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>1.139</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.322</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1811,7 +1671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1852,17 +1712,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_18_41_11_case08_T18_P0.png</t>
+          <t>2026_07_14_18_35_38_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32.039</v>
+        <v>32.201</v>
       </c>
       <c r="D2" t="n">
-        <v>37.01</v>
+        <v>34.54</v>
       </c>
       <c r="E2" t="n">
-        <v>1.208</v>
+        <v>1.253</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -1872,17 +1732,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_32_35_11_case08_T18_P0.png</t>
+          <t>2026_07_14_18_50_02_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32.039</v>
+        <v>32.345</v>
       </c>
       <c r="D3" t="n">
-        <v>38.23</v>
+        <v>33.18</v>
       </c>
       <c r="E3" t="n">
-        <v>1.181</v>
+        <v>1.186</v>
       </c>
       <c r="F3" t="inlineStr"/>
     </row>
@@ -1892,17 +1752,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_49_02_11_case08_T18_P0.png</t>
+          <t>2026_07_14_19_52_41_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32.412</v>
+        <v>32.261</v>
       </c>
       <c r="D4" t="n">
-        <v>37.85</v>
+        <v>33</v>
       </c>
       <c r="E4" t="n">
-        <v>1.221</v>
+        <v>1.134</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -1912,17 +1772,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_10_03_06_11_case08_T18_P0.png</t>
+          <t>2026_07_15_07_48_47_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32.281</v>
+        <v>31.986</v>
       </c>
       <c r="D5" t="n">
-        <v>38.17</v>
+        <v>35.78</v>
       </c>
       <c r="E5" t="n">
-        <v>1.236</v>
+        <v>1.295</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -1932,39 +1792,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_17_27_11_case08_T18_P0.png</t>
+          <t>2026_07_15_08_05_52_11_case08_T18_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.369</v>
+        <v>32.047</v>
       </c>
       <c r="D6" t="n">
-        <v>35.62</v>
+        <v>35.55</v>
       </c>
       <c r="E6" t="n">
-        <v>1.203</v>
+        <v>1.187</v>
       </c>
       <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_31_37_11_case08_T18_P0.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>32.247</v>
-      </c>
-      <c r="D7" t="n">
-        <v>35.73</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1977,7 +1817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2018,17 +1858,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_19_26_11_case09_T22_P1.png</t>
+          <t>2026_07_14_18_36_27_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.311</v>
+        <v>23.151</v>
       </c>
       <c r="D2" t="n">
-        <v>37.65</v>
+        <v>34.3</v>
       </c>
       <c r="E2" t="n">
-        <v>1.555</v>
+        <v>1.615</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -2038,17 +1878,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_33_19_11_case09_T22_P1.png</t>
+          <t>2026_07_14_18_50_50_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.313</v>
+        <v>23.251</v>
       </c>
       <c r="D3" t="n">
-        <v>36.65</v>
+        <v>34.87</v>
       </c>
       <c r="E3" t="n">
-        <v>1.528</v>
+        <v>1.533</v>
       </c>
       <c r="F3" t="inlineStr"/>
     </row>
@@ -2058,17 +1898,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_49_47_11_case09_T22_P1.png</t>
+          <t>2026_07_14_19_53_29_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.545</v>
+        <v>23.195</v>
       </c>
       <c r="D4" t="n">
-        <v>26.92</v>
+        <v>33.46</v>
       </c>
       <c r="E4" t="n">
-        <v>1.562</v>
+        <v>1.498</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -2078,17 +1918,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_10_03_51_11_case09_T22_P1.png</t>
+          <t>2026_07_15_07_49_36_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.469</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>37.29</v>
+        <v>35.12</v>
       </c>
       <c r="E5" t="n">
-        <v>1.572</v>
+        <v>1.7</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -2098,39 +1938,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_18_11_11_case09_T22_P1.png</t>
+          <t>2026_07_15_08_06_41_11_case09_T22_P1.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.518</v>
+        <v>23.037</v>
       </c>
       <c r="D6" t="n">
-        <v>37.86</v>
+        <v>35.6</v>
       </c>
       <c r="E6" t="n">
-        <v>1.544</v>
+        <v>1.553</v>
       </c>
       <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_32_21_11_case09_T22_P1.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>20.443</v>
-      </c>
-      <c r="D7" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.641</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2143,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2184,21 +2004,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026_07_11_09_20_15_11_case11_T28_P0.png</t>
+          <t>2026_07_14_18_37_15_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.741</v>
+        <v>23.025</v>
       </c>
       <c r="D2" t="n">
-        <v>34.8</v>
+        <v>33.88</v>
       </c>
       <c r="E2" t="n">
-        <v>1.569</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.907</v>
-      </c>
+        <v>1.634</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2206,21 +2024,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026_07_11_09_34_08_11_case11_T28_P0.png</t>
+          <t>2026_07_14_18_51_39_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.745</v>
+        <v>23.134</v>
       </c>
       <c r="D3" t="n">
-        <v>36.62</v>
+        <v>32.37</v>
       </c>
       <c r="E3" t="n">
-        <v>1.536</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.907</v>
-      </c>
+        <v>1.539</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2228,21 +2044,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026_07_11_09_50_36_11_case11_T28_P0.png</t>
+          <t>2026_07_14_19_54_18_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.994</v>
+        <v>23.064</v>
       </c>
       <c r="D4" t="n">
-        <v>25.38</v>
+        <v>32.35</v>
       </c>
       <c r="E4" t="n">
-        <v>1.601</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.907</v>
-      </c>
+        <v>1.49</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2250,21 +2064,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026_07_11_10_04_39_11_case11_T28_P0.png</t>
+          <t>2026_07_15_07_50_24_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.908</v>
+        <v>22.879</v>
       </c>
       <c r="D5" t="n">
-        <v>36.84</v>
+        <v>34.2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.596</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.907</v>
-      </c>
+        <v>1.656</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2272,43 +2084,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026_07_11_10_19_00_11_case11_T28_P0.png</t>
+          <t>2026_07_15_08_07_29_11_case11_T28_P0.png</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.963</v>
+        <v>22.922</v>
       </c>
       <c r="D6" t="n">
-        <v>39.49</v>
+        <v>35.6</v>
       </c>
       <c r="E6" t="n">
-        <v>1.584</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.907</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026_07_11_10_33_10_11_case11_T28_P0.png</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="D7" t="n">
-        <v>36.75</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.678</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.907</v>
-      </c>
+        <v>1.569</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
